--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -799,21 +799,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7589</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -832,21 +832,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -865,21 +865,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -898,21 +898,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -931,21 +931,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -964,21 +964,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -997,21 +997,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1129,21 +1129,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1195,21 +1195,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1261,21 +1261,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1294,21 +1294,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1327,21 +1327,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1360,21 +1360,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1393,21 +1393,21 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1426,21 +1426,21 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1419</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1459,23 +1459,27 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1624,23 +1628,27 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1921,21 +1929,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1987,21 +1995,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2020,21 +2028,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2053,21 +2061,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2086,21 +2094,21 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2218,21 +2226,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2251,23 +2259,27 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2383,21 +2395,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2416,21 +2428,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2449,21 +2461,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2482,23 +2494,27 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2515,21 +2531,21 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2548,21 +2564,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2581,21 +2597,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2614,21 +2630,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2647,21 +2663,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2779,21 +2795,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2845,21 +2861,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2878,21 +2894,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3010,21 +3026,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3043,21 +3059,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3076,21 +3092,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3142,21 +3158,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3175,21 +3191,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3208,21 +3224,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3241,21 +3257,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3274,21 +3290,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3307,21 +3323,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -3340,21 +3356,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -3472,21 +3488,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3505,23 +3521,27 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3538,21 +3558,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3571,21 +3591,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3604,21 +3624,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3637,21 +3657,21 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3670,23 +3690,27 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Bacenta Sum</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Colossians 1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +454,166 @@
         <is>
           <t>No. Of Services</t>
         </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Isaac Agyeman</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Colossians 1</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>'Colossians 1'!C4</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>'Colossians 1'!D4</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>'Colossians 1'!E4</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>'Colossians 1'!F4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Colossians 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Haatso Mabey</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Malcolm Otchere - Forbih</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7647</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>SUM(C3:C3)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>SUM(D3:D3)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUM(E3:E3)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>SUM(F3:F3)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>F4&amp;"/"&amp;C4</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>SUM(H3:H3)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -567,21 +567,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>7647</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -9,6 +9,15 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Colossians 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Colossians 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Colossians 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Galatians 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Galatians 2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Galatians 2 (Hold)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Galatians 4" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 5" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 9" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,19 +477,931 @@
         </is>
       </c>
       <c r="C3">
-        <f>'Colossians 1'!C4</f>
+        <f>'Colossians 1'!C14</f>
         <v/>
       </c>
       <c r="D3">
-        <f>'Colossians 1'!D4</f>
+        <f>'Colossians 1'!D14</f>
         <v/>
       </c>
       <c r="E3">
-        <f>'Colossians 1'!E4</f>
+        <f>'Colossians 1'!E14</f>
         <v/>
       </c>
       <c r="F3">
-        <f>'Colossians 1'!F4</f>
+        <f>'Colossians 1'!F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Edwin Ogoe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Colossians 2</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>'Colossians 2'!C12</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>'Colossians 2'!D12</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>'Colossians 2'!E12</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>'Colossians 2'!F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nathan Kudowor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Colossians 3</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>'Colossians 3'!C8</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>'Colossians 3'!D8</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>'Colossians 3'!E8</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>'Colossians 3'!F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Isaac Agyeman</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Galatians 1</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>'Galatians 1'!C6</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>'Galatians 1'!D6</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>'Galatians 1'!E6</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>'Galatians 1'!F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Richmond Annan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Galatians 2</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>'Galatians 2'!C12</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>'Galatians 2'!D12</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>'Galatians 2'!E12</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>'Galatians 2'!F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Edwin Ogoe</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Galatians 2 (Hold)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>'Galatians 2 (Hold)'!C6</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>'Galatians 2 (Hold)'!D6</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>'Galatians 2 (Hold)'!E6</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>'Galatians 2 (Hold)'!F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Eric Boachie Yiadom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Galatians 4</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>'Galatians 4'!C8</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>'Galatians 4'!D8</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>'Galatians 4'!E8</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>'Galatians 4'!F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Galatians 5</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>'Galatians 5'!C14</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>'Galatians 5'!D14</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>'Galatians 5'!E14</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>'Galatians 5'!F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>'Galatians 8'!C10</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>'Galatians 8'!D10</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>'Galatians 8'!E10</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>'Galatians 8'!F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Galatians 9</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>'Galatians 9'!C10</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>'Galatians 9'!D10</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>'Galatians 9'!E10</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>'Galatians 9'!F10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKUAFO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Foanor Alloh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tracy Osei</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nana Ahema Forson</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jennifer Wordi</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Volta Mega</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Doris Ainooh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UPSA Allos 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Papa Kojo Amoakwa</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UPSA Allos 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Herbert Aidoo</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UPSA Allos 3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marvellous Korsoku</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UPSA Allos 4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Linda Tunkum</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UPSA Allos 5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joshua Agymang</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UPSA Allos 6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>David Abuaku</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UPSA Allos 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blessing Umukoro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -495,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,12 +1476,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haatso Mabey</t>
+          <t>Family Health</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Malcolm Otchere - Forbih</t>
+          <t>David Yalleh</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -588,31 +1509,2523 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Family Health Teshie</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Obed Owusu</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Haatso Mabey</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Malcolm Otchere - Forbih</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hatso TBC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Zenas Adarkwah Yiadom</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pantang Campus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Princess Gueyennevievarl Wilson-Anderson</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pantang Town</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abraham Koney</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>THS Agbogba</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Raymond Agboola</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>THS Bohye</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Christian Ocquaye</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>THS Ecomog</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alex Baah-Gyambrah</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Samuel Umerah</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wisconsin Fruitful</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Thomas Dodoo</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4">
-        <f>SUM(C3:C3)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>SUM(D3:D3)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>SUM(E3:E3)</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>SUM(F3:F3)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>F4&amp;"/"&amp;C4</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>SUM(H3:H3)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Colossians 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Abundant Life North</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eunice Ashiagbor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Abundant Life South</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Elorm Agbesinyale</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Abundant Life West</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eshal Gabriel</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vicentia Boakye</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Deacon's Academy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gideon Boateng</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dome Central</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Samuel Brown</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dome Main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>John Amoako</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dome Ministries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wilhermina Teprey</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dome North</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pearl Addo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Colossians 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Colossians Ablekuma</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jude Yamoah</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Haatso Central</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joel Bartels Asante</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Haatso West</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Michael Sarpong</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kissieman</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Oliver Agbenyegah</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>THS Westland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joseph Halivor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>F8&amp;"/"&amp;C8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUM(H3:H7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nii Nkunim Armar</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACM 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Daniel Orleans-Lindsay</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Limann</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Accra City Church</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ishmael Oplerm</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adabraka</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Candy Mensah</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Zephaniah Lartey</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ATU Church</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>James Pekyie</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATU Main Campus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Racheal Boamah</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>City Campus</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abednego Abbey</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jamestown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Humphrey Quaye</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Yours and Ours</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 2 (Hold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ATU On Campus</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Korle Bu A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Legon City</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UPSA Campus Hostels</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Andrew Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Upsa Diaspora</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bright Nurtey Tettey Tetteh</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UPSA Green Hostel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Desmond Hlorgbey</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UPSA Hostels A &amp; B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jayson Quarshie</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UPSA Rawlings Hostel</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Eric Boachie Yiadom</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>F8&amp;"/"&amp;C8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUM(H3:H7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lawrence Adetunji</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AIT Yeshua</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jonathan Ekhagbai</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aparche</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cyrus-Dag Stephens</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Encephal College of Health</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Samuel Tigah</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Galilea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lady Vanessa Osei</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GTUC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Richard Manu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GTUC Allos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kings/Regent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0/9</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -476,21 +476,17 @@
           <t>Colossians 1</t>
         </is>
       </c>
-      <c r="C3">
-        <f>'Colossians 1'!C14</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>'Colossians 1'!D14</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>'Colossians 1'!E14</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>'Colossians 1'!F14</f>
-        <v/>
+      <c r="C3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3951</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -504,21 +500,17 @@
           <t>Colossians 2</t>
         </is>
       </c>
-      <c r="C4">
-        <f>'Colossians 2'!C12</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>'Colossians 2'!D12</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>'Colossians 2'!E12</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>'Colossians 2'!F12</f>
-        <v/>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -532,21 +524,17 @@
           <t>Colossians 3</t>
         </is>
       </c>
-      <c r="C5">
-        <f>'Colossians 3'!C8</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>'Colossians 3'!D8</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>'Colossians 3'!E8</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>'Colossians 3'!F8</f>
-        <v/>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>645</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -560,21 +548,17 @@
           <t>Galatians 1</t>
         </is>
       </c>
-      <c r="C6">
-        <f>'Galatians 1'!C6</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>'Galatians 1'!D6</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>'Galatians 1'!E6</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>'Galatians 1'!F6</f>
-        <v/>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>212</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -588,21 +572,17 @@
           <t>Galatians 2</t>
         </is>
       </c>
-      <c r="C7">
-        <f>'Galatians 2'!C12</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>'Galatians 2'!D12</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>'Galatians 2'!E12</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>'Galatians 2'!F12</f>
-        <v/>
+      <c r="C7" t="n">
+        <v>39</v>
+      </c>
+      <c r="D7" t="n">
+        <v>159</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F7" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -616,21 +596,17 @@
           <t>Galatians 2 (Hold)</t>
         </is>
       </c>
-      <c r="C8">
-        <f>'Galatians 2 (Hold)'!C6</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>'Galatians 2 (Hold)'!D6</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>'Galatians 2 (Hold)'!E6</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>'Galatians 2 (Hold)'!F6</f>
-        <v/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -644,21 +620,17 @@
           <t>Galatians 4</t>
         </is>
       </c>
-      <c r="C9">
-        <f>'Galatians 4'!C8</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>'Galatians 4'!D8</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>'Galatians 4'!E8</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>'Galatians 4'!F8</f>
-        <v/>
+      <c r="C9" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" t="n">
+        <v>62</v>
+      </c>
+      <c r="E9" t="n">
+        <v>705</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -672,21 +644,17 @@
           <t>Galatians 5</t>
         </is>
       </c>
-      <c r="C10">
-        <f>'Galatians 5'!C14</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>'Galatians 5'!D14</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>'Galatians 5'!E14</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>'Galatians 5'!F14</f>
-        <v/>
+      <c r="C10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D10" t="n">
+        <v>151</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3022</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -700,21 +668,17 @@
           <t>Galatians 8</t>
         </is>
       </c>
-      <c r="C11">
-        <f>'Galatians 8'!C10</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>'Galatians 8'!D10</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>'Galatians 8'!E10</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>'Galatians 8'!F10</f>
-        <v/>
+      <c r="C11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D11" t="n">
+        <v>118</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2806</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -728,21 +692,17 @@
           <t>Galatians 9</t>
         </is>
       </c>
-      <c r="C12">
-        <f>'Galatians 9'!C10</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>'Galatians 9'!D10</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>'Galatians 9'!E10</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>'Galatians 9'!F10</f>
-        <v/>
+      <c r="C12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>64</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1923</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -825,24 +785,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -858,24 +818,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -891,24 +851,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -927,21 +887,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -953,28 +913,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jennifer Wordi</t>
+          <t>Yosi Forson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -990,24 +950,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1215</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>8/11</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1023,24 +983,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>5/4</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1086,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,21 +1118,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1191,21 +1151,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1224,21 +1184,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1257,21 +1217,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1290,21 +1250,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1323,21 +1283,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1356,52 +1316,85 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>UPSA Allos 8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/10</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -1488,21 +1481,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1521,21 +1514,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1554,21 +1547,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3253</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1587,21 +1580,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1653,21 +1646,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1686,21 +1679,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1752,21 +1745,21 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1785,21 +1778,21 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1818,21 +1811,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1950,21 +1943,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1983,21 +1976,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2016,21 +2009,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2049,21 +2042,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2082,21 +2075,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2148,21 +2141,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2181,21 +2174,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2214,21 +2207,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2412,21 +2405,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2445,21 +2438,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2478,21 +2471,21 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2610,21 +2603,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2643,21 +2636,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2732,7 +2725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2792,16 +2785,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accra City Church</t>
+          <t>Accra City</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Ferdinand Adams</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2814,11 +2807,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2830,11 +2823,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Candy Mensah</t>
+          <t>Prince Agbesi</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2847,11 +2840,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2867,40 +2860,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>Arena Allos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Eric Akoto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2913,73 +2906,73 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2990,130 +2983,196 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humphrey Quaye</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emmanuel Otiboe</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>120</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yours and Ours</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>466</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -3386,21 +3445,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3419,21 +3478,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3452,21 +3511,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3485,21 +3544,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3650,21 +3709,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3683,21 +3742,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3716,21 +3775,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3749,21 +3808,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3782,21 +3841,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3815,21 +3874,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3848,21 +3907,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3881,21 +3940,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3914,21 +3973,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3947,21 +4006,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -3980,21 +4039,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -14,10 +14,13 @@
     <sheet name="Galatians 1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Galatians 2" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Galatians 2 (Hold)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Galatians 4" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 5" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 6 A" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 7" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 8" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 9" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,13 +483,13 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>3951</v>
+        <v>3976</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -612,96 +615,168 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>705</v>
+        <v>582</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
-        <v>3022</v>
+        <v>705</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="E11" t="n">
-        <v>2806</v>
+        <v>3022</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Galatians 6 A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" t="n">
+        <v>102</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2721</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>55</v>
+      </c>
+      <c r="D13" t="n">
+        <v>298</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2453</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
+        <v>118</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2806</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Divine Olubakinde</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Galatians 9</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C15" t="n">
         <v>27</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>64</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E15" t="n">
         <v>1923</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -716,13 +791,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 5</t>
         </is>
       </c>
     </row>
@@ -776,262 +851,394 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>512</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>18</v>
-      </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>GTUC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Richard Manu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>1215</v>
+        <v>1050</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>407</v>
+        <v>806</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/4</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>73</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kings/Regent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>588</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>135</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -1041,6 +1248,1722 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 6 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Akuafo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Karyn Tagoe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bani</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kojo Afriyie</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1887</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Block A Annex</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marcia Adomako</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>115</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Block B Annex</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kevin Brown</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Commonwealth</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peter Tefuttor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Emelda Antwi-Agyei</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Evandy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Delali Apedu</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Evandy Annex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Caroline Hammond</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pent B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yves Mensah</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>220</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pent C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Roland Cudjoe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>185</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Elizabeth Obeng Adu</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TF Annex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stephanie Seglah</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Volta Annex</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>SUM(C3:C17)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>SUM(D3:D17)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>SUM(E3:E17)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>SUM(F3:F17)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>F18&amp;"/"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(H3:H17)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fredrick Anokye</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dacosta Amponsah</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Area 1  Logos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Commonwealth 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lois Osei</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Commonwealth 2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>David Arhin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deborah Wiredu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abena Kyeremaa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jesus Night TF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jochebed Lawson-Heymann</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kwapong</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eunice Owusu</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Legon Hall</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Edberg Ayensu</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Main Campus Allos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>143</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1565</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Main Campus Charis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Stephen Asare Osei</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Main Campus Dunamis</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nana Kwame Barima</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Main Campus Hagios</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Philmorra Laryea Okorley</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>146</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>107</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>SUM(C3:C23)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>SUM(D3:D23)</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>SUM(E3:E23)</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>SUM(F3:F23)</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>F24&amp;"/"&amp;C24</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>SUM(H3:H23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKUAFO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Foanor Alloh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>314</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tracy Osei</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nana Ahema Forson</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>223</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yosi Forson</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1215</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Volta Mega</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Doris Ainooh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>407</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5/4</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1679,21 +3602,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3373,13 +5296,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 3</t>
         </is>
       </c>
     </row>
@@ -3433,148 +5356,148 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>Campus Anagkazo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Nayram Gblorkpor</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>Limann Governorship</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Gerald Essuman</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Main Campus Poimen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Theodora Waguena</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>375</v>
+        <v>175</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UPSA Rawlings Hostel</t>
+          <t>Prince of Peace</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3587,42 +5510,141 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Revelations</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Edna Adorshie</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>147</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8">
-        <f>SUM(C3:C7)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E3:E7)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>SUM(F3:F7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>F8&amp;"/"&amp;C8</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>SUM(H3:H7)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -3637,13 +5659,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 4</t>
         </is>
       </c>
     </row>
@@ -3697,52 +5719,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
@@ -3752,339 +5774,141 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>UPSA Rawlings Hostel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Richard Manu</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GTUC Allos</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Michael Oteng</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>23</v>
-      </c>
-      <c r="E9" t="n">
-        <v>806</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GTUC Allos 3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sylvester Ntumy</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" t="n">
-        <v>53</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GTUC Main Campus</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Jeremiah Ashong</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E11" t="n">
-        <v>73</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Kings/Regent</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>588</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Korle Bu Light</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Sonia Elolo</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>27</v>
-      </c>
-      <c r="E13" t="n">
-        <v>135</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>F8&amp;"/"&amp;C8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUM(H3:H7)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -11,16 +11,18 @@
     <sheet name="Colossians 1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Colossians 2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Colossians 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Galatians 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Galatians 2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Galatians 2 (Hold)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Galatians 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 6 A" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 7" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 8" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 9" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Colossians 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 2 (Hold)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +482,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>3976</v>
+        <v>205</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -504,22 +506,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E4" t="n">
-        <v>1377</v>
+        <v>2829</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nathan Kudowor</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -528,37 +530,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E5" t="n">
-        <v>645</v>
+        <v>1020</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Isaac Agyeman</t>
+          <t>Malcolm Otchere - Forbih</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
+          <t>Colossians 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>212</v>
+        <v>3489</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -567,217 +569,265 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Richmond Annan</t>
+          <t>Abraham Koney</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Galatians 2</t>
+          <t>Colossians 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>2260</v>
+        <v>1009</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Edwin Ogoe</t>
+          <t>Isaac Agyeman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Richmond Annan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="E9" t="n">
-        <v>582</v>
+        <v>3292</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Edwin Ogoe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 2 (Hold)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="E11" t="n">
-        <v>3022</v>
+        <v>1377</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>2721</v>
+        <v>490</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>298</v>
+        <v>94</v>
       </c>
       <c r="E13" t="n">
-        <v>2453</v>
+        <v>2035</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>2806</v>
+        <v>5222</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>55</v>
+      </c>
+      <c r="D15" t="n">
+        <v>204</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1576</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>109</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1708</v>
+      </c>
+      <c r="F16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Divine Olubakinde</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Galatians 9</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="n">
-        <v>64</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F15" t="n">
-        <v>15</v>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" t="n">
+        <v>101</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3685</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -791,13 +841,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 3</t>
         </is>
       </c>
     </row>
@@ -851,121 +901,121 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Campus Anagkazo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Nayram Gblorkpor</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -983,262 +1033,130 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Revelations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Edna Adorshie</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>Sarbah</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>1050</v>
+        <v>225</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Sey</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Dennis Kpogli</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>806</v>
+        <v>855</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sylvester Ntumy</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" t="n">
-        <v>53</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GTUC Main Campus</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Jeremiah Ashong</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E11" t="n">
-        <v>73</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Kings/Regent</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>588</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Korle Bu Light</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Sonia Elolo</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>27</v>
-      </c>
-      <c r="E13" t="n">
-        <v>135</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -1253,13 +1171,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 4</t>
         </is>
       </c>
     </row>
@@ -1313,161 +1231,161 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1887</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>345</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>UPSA Rawlings Hostel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1478,361 +1396,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Emelda Antwi-Agyei</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Evandy</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Delali Apedu</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E9" t="n">
-        <v>99</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Evandy Annex</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Caroline Hammond</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pent B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Yves Mensah</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>220</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pent C</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Roland Cudjoe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pent Old &amp; A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>22</v>
-      </c>
-      <c r="E13" t="n">
-        <v>185</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Elizabeth Obeng Adu</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TF Annex</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Samuel Boateng</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Stephanie Seglah</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>65</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Volta Annex</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18">
-        <f>SUM(C3:C17)</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>SUM(D3:D17)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>SUM(E3:E17)</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>SUM(F3:F17)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>F18&amp;"/"&amp;C18</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>SUM(H3:H17)</f>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>F8&amp;"/"&amp;C8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUM(H3:H7)</f>
         <v/>
       </c>
     </row>
@@ -1847,13 +1435,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 5</t>
         </is>
       </c>
     </row>
@@ -1907,16 +1495,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 1</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fredrick Anokye</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1929,99 +1517,99 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Hall 2</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dacosta Amponsah</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -2039,161 +1627,161 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 2</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>GTUC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Richard Manu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jesus Night TF</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2204,29 +1792,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Kings/Regent</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>725</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2237,394 +1825,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>1565</v>
+        <v>105</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Campus Charis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Stephen Asare Osei</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Dunamis</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nana Kwame Barima</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>35</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main Campus Hagios</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Philmorra Laryea Okorley</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>13</v>
-      </c>
-      <c r="E16" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Main Campus Parakletos</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Melissa Meledi</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>18</v>
-      </c>
-      <c r="E18" t="n">
-        <v>146</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>80</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>12</v>
-      </c>
-      <c r="E21" t="n">
-        <v>107</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24">
-        <f>SUM(C3:C23)</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>SUM(D3:D23)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>SUM(E3:E23)</f>
-        <v/>
-      </c>
-      <c r="F24">
-        <f>SUM(F3:F23)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>F24&amp;"/"&amp;C24</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>SUM(H3:H23)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -2639,13 +1897,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
     </row>
@@ -2699,29 +1957,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>512</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2732,22 +1990,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>4040</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -2765,95 +2023,95 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2864,62 +2122,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Diamond Jubilee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>1215</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>407</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2930,31 +2188,295 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Evandy Annex New</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Caroline Hammond</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pent B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yves Mensah</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>220</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pent C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Roland Cudjoe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>291</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Elizabeth Obeng Adu</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stephanie Seglah</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C18">
+        <f>SUM(C3:C17)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>SUM(D3:D17)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>SUM(E3:E17)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>SUM(F3:F17)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>F18&amp;"/"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(H3:H17)</f>
         <v/>
       </c>
     </row>
@@ -2969,13 +2491,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 9</t>
+          <t>Galatians 7</t>
         </is>
       </c>
     </row>
@@ -3029,22 +2551,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Allos 1</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Papa Kojo Amoakwa</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>1456</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -3062,6 +2584,1194 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Akuafo Hall 1 New</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fredrick Anokye</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 2 New</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dacosta Amponsah</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Area 1  Logos</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Commonwealth 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lois Osei</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Commonwealth 2 New</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>David Arhin</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deborah Wiredu</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Abena Kyeremaa</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jesus Night TF New</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jochebed Lawson-Heymann</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kwapong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Eunice Owusu</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>205</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Legon Hall</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Edberg Ayensu</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Main Campus Allos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Main Campus Dunamis</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nana Kwame Barima</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Main Campus Hagios</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Philmorra Laryea Okorley</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>250</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>SUM(C3:C23)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>SUM(D3:D23)</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>SUM(E3:E23)</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>SUM(F3:F23)</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>F24&amp;"/"&amp;C24</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>SUM(H3:H23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKUAFO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Foanor Alloh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ruby Nelson</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>309</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tracy Osei</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nana Ahema Forson</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>51</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yosi Forson</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Volta Mega</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Doris Ainooh</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>193</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Volta Others</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rachael Sekyiwaaa</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Galatians 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UPSA Allos 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Papa Kojo Amoakwa</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>273</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>UPSA Allos 2</t>
         </is>
       </c>
@@ -3071,24 +3781,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3104,20 +3814,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3137,24 +3847,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3173,10 +3883,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3203,24 +3913,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3236,24 +3946,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3269,55 +3979,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2551</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>UPSA Allos 9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chris Keelson</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>135</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3332,7 +4075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3404,21 +4147,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3437,10 +4180,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3458,328 +4201,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Haatso Mabey</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Malcolm Otchere - Forbih</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3253</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hatso TBC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Zenas Adarkwah Yiadom</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>72</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pantang Campus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Princess Gueyennevievarl Wilson-Anderson</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pantang Town</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Abraham Koney</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>180</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>THS Agbogba</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Raymond Agboola</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>45</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2/7</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>THS Bohye</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Christian Ocquaye</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>THS Ecomog</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Alex Baah-Gyambrah</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Samuel Umerah</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E12" t="n">
-        <v>75</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Wisconsin Fruitful</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Thomas Dodoo</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" t="n">
-        <v>81</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C5">
+        <f>SUM(C3:C4)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUM(D3:D4)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUM(E3:E4)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUM(F3:F4)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>F5&amp;"/"&amp;C5</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUM(H3:H4)</f>
         <v/>
       </c>
     </row>
@@ -3794,7 +4240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3866,10 +4312,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3896,24 +4342,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3932,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
@@ -3965,21 +4411,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4001,7 +4447,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -4019,29 +4465,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dome Central</t>
+          <t>Dome Main</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Samuel Brown</t>
+          <t>John Amoako</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4052,62 +4498,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dome Main</t>
+          <t>Dome Ministries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>John Amoako</t>
+          <t>Wilhermina Teprey</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>1110</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dome Ministries</t>
+          <t>Dome North</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wilhermina Teprey</t>
+          <t>Pearl Addo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>870</v>
+        <v>399</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4118,29 +4564,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dome North</t>
+          <t>Taifa Burkina</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pearl Addo</t>
+          <t>Samuel Brown</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -4151,31 +4597,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>465</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -4190,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4295,109 +4765,109 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Haatso West</t>
+          <t>Haatso Executive</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Michael Sarpong</t>
+          <t>Stephen Mensah</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kissieman</t>
+          <t>Haatso Melcom</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oliver Agbenyegah</t>
+          <t>Kenneth Koomson</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>THS Westland</t>
+          <t>Haatso Palace</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joseph Halivor</t>
+          <t>Richard Anku</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4415,31 +4885,97 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Haatso West</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Michael Sarpong</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>760</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>THS Westland</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Joseph Halivor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>130</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8">
-        <f>SUM(C3:C7)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E3:E7)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>SUM(F3:F7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>F8&amp;"/"&amp;C8</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>SUM(H3:H7)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -4460,7 +4996,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
+          <t>Colossians 4</t>
         </is>
       </c>
     </row>
@@ -4514,62 +5050,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>Haatso Mabey</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nii Nkunim Armar</t>
+          <t>Malcolm Otchere - Forbih</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3254</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>52</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACM 2</t>
+          <t>Hatso TBC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daniel Orleans-Lindsay</t>
+          <t>Zenas Adarkwah Yiadom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4580,29 +5116,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Limann</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>THS Ecomog</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alex Baah-Gyambrah</t>
+        </is>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4648,13 +5188,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 2</t>
+          <t>Colossians 5</t>
         </is>
       </c>
     </row>
@@ -4708,16 +5248,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accra City</t>
+          <t>Pantang Campus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ferdinand Adams</t>
+          <t>Princess Gueyennevievarl Wilson-Anderson</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -4730,106 +5270,106 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adabraka</t>
+          <t>Pantang Town</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Agbesi</t>
+          <t>Abraham Koney</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>THS Agbogba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zephaniah Lartey</t>
+          <t>Raymond Agboola</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arena Allos</t>
+          <t>THS Bohye</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eric Akoto</t>
+          <t>Christian Ocquaye</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4840,262 +5380,97 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Samuel Umerah</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>Wisconsin Fruitful</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Thomas Dodoo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>City Campus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Abednego Abbey</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" t="n">
-        <v>375</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Jamestown</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Joel Quartey</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>65</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jamestown Allos</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ishmael Oplerm</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" t="n">
-        <v>909</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UssherFort</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Seth Kpelebe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>23</v>
-      </c>
-      <c r="E12" t="n">
-        <v>120</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Emmanuel Otiboe</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>30</v>
-      </c>
-      <c r="E13" t="n">
-        <v>466</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C9">
+        <f>SUM(C3:C8)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUM(D3:D8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E3:E8)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>F9&amp;"/"&amp;C9</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUM(H3:H8)</f>
         <v/>
       </c>
     </row>
@@ -5110,13 +5485,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 1</t>
         </is>
       </c>
     </row>
@@ -5170,41 +5545,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ATU On Campus</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nii Nkunim Armar</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Korle Bu A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>ACM 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Daniel Orleans-Lindsay</t>
+        </is>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -5217,36 +5600,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Legon City</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>ACM 3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joan Obakpolor</t>
+        </is>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5257,31 +5644,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Limann</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6">
-        <f>SUM(C3:C5)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>SUM(D3:D5)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>SUM(E3:E5)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>SUM(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>F6&amp;"/"&amp;C6</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>SUM(H3:H5)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -5296,13 +5712,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 2</t>
         </is>
       </c>
     </row>
@@ -5356,29 +5772,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>Accra City</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Ferdinand Adams</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -5389,16 +5805,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Limann Governorship</t>
+          <t>Adabraka</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gerald Essuman</t>
+          <t>Prince Agbesi</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -5411,40 +5827,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Main Campus Poimen</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Theodora Waguena</t>
+          <t>Zephaniah Lartey</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>105</v>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5455,29 +5871,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>Arena Allos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Eric Akoto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5488,29 +5904,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Prince of Peace</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5521,55 +5937,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Revelations</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edna Adorshie</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sarbah</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>147</v>
+        <v>365</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -5587,29 +6003,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sey</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -5620,31 +6036,130 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Jamestown Allos</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ishmael Oplerm</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>58</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5/4</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>165</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yours and Ours</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>160</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -5659,13 +6174,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 2 (Hold)</t>
         </is>
       </c>
     </row>
@@ -5719,196 +6234,118 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Andrew Heward-Mills</t>
-        </is>
-      </c>
+          <t>ATU On Campus</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
-        </is>
-      </c>
+          <t>Korle Bu A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Desmond Hlorgbey</t>
-        </is>
-      </c>
+          <t>Legon City</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jayson Quarshie</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" t="n">
-        <v>375</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>UPSA Rawlings Hostel</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Eric Boachie Yiadom</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8">
-        <f>SUM(C3:C7)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E3:E7)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>SUM(F3:F7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>F8&amp;"/"&amp;C8</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>SUM(H3:H7)</f>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -485,13 +485,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F4" t="n">
         <v>26</v>
-      </c>
-      <c r="D4" t="n">
-        <v>98</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2829</v>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +533,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>1020</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -557,13 +557,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>3489</v>
+        <v>2688</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -581,13 +581,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>1009</v>
+        <v>2352</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -605,10 +605,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>440</v>
+        <v>206</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="E9" t="n">
-        <v>3292</v>
+        <v>3377</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -677,10 +677,10 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E11" t="n">
-        <v>1377</v>
+        <v>656</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
@@ -701,13 +701,13 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -725,13 +725,13 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E13" t="n">
-        <v>2035</v>
+        <v>2099</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -749,10 +749,10 @@
         <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E14" t="n">
-        <v>5222</v>
+        <v>2033</v>
       </c>
       <c r="F14" t="n">
         <v>38</v>
@@ -773,13 +773,13 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="E15" t="n">
-        <v>1576</v>
+        <v>1334</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="E16" t="n">
-        <v>1708</v>
+        <v>3369</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -821,13 +821,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E17" t="n">
-        <v>3685</v>
+        <v>1294</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
         <v>15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -982,7 +982,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -1012,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1045,10 +1045,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1078,10 +1078,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
@@ -1111,10 +1111,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>855</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,21 +1243,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1309,21 +1309,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1342,10 +1342,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1363,64 +1363,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UPSA Rawlings Hostel</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Eric Boachie Yiadom</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8">
-        <f>SUM(C3:C7)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E3:E7)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>SUM(F3:F7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>F8&amp;"/"&amp;C8</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>SUM(H3:H7)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -1507,21 +1474,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1540,10 +1507,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1573,21 +1540,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1606,7 +1573,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>50</v>
@@ -1639,21 +1606,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1672,21 +1639,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>1125</v>
       </c>
       <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1705,21 +1672,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1738,10 +1705,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>620</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1771,21 +1738,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1807,7 +1774,7 @@
         <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>725</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1837,21 +1804,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1972,7 +1939,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -2005,7 +1972,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>4040</v>
+        <v>203</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -2035,10 +2002,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -2068,10 +2035,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -2101,10 +2068,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -2134,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -2167,10 +2134,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -2200,21 +2167,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2233,10 +2200,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -2266,21 +2233,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -2299,10 +2266,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>291</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -2365,10 +2332,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -2398,10 +2365,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -2434,7 +2401,7 @@
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2560,20 +2527,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2593,24 +2560,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2629,10 +2596,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -2695,7 +2662,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>40</v>
@@ -2728,21 +2695,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2761,21 +2728,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2794,10 +2761,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -2824,20 +2791,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2863,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -2890,20 +2857,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2923,20 +2890,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2959,21 +2926,21 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2995,18 +2962,18 @@
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -3025,10 +2992,10 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -3058,10 +3025,10 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -3091,21 +3058,21 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr"/>
     </row>
@@ -3124,21 +3091,21 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr"/>
     </row>
@@ -3154,20 +3121,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3190,17 +3157,17 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3223,21 +3190,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr"/>
     </row>
@@ -3283,7 +3250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3355,21 +3322,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>900</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3388,21 +3355,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3421,21 +3388,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>309</v>
+        <v>245</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3454,21 +3421,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3487,21 +3454,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3520,21 +3487,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3550,24 +3517,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>500</v>
+        <v>1642</v>
       </c>
       <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3586,21 +3553,21 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>193</v>
+        <v>447</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3619,52 +3586,76 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>135</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3751,21 +3742,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3781,24 +3772,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3817,10 +3808,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3850,10 +3841,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -3883,10 +3874,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3916,10 +3907,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -3946,24 +3937,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3982,10 +3973,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>2551</v>
+        <v>374</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4015,10 +4006,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -4147,21 +4138,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4180,10 +4171,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4312,10 +4303,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4342,24 +4333,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4378,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
@@ -4411,21 +4402,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4441,20 +4432,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4477,10 +4468,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>365</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4510,10 +4501,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>1110</v>
+        <v>295</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4540,20 +4531,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>399</v>
+        <v>200</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4564,22 +4555,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Taifa Burkina</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Samuel Brown</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>693</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4597,26 +4588,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Taifa Burkina</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Samuel Brown</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>465</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4765,10 +4765,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4831,21 +4831,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4864,10 +4864,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4900,7 +4900,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -4930,21 +4930,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5062,10 +5062,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>3254</v>
+        <v>2498</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -5095,10 +5095,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5128,21 +5128,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5293,10 +5293,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>670</v>
+        <v>371</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5326,21 +5326,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5359,10 +5359,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -5392,10 +5392,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>1635</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -5425,21 +5425,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5485,7 +5485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5557,21 +5557,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5590,21 +5590,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5623,10 +5623,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -5644,60 +5644,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Limann</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7">
-        <f>SUM(C3:C6)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>SUM(D3:D6)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>SUM(E3:E6)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>SUM(F3:F6)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>F7&amp;"/"&amp;C7</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>SUM(H3:H6)</f>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
         <v/>
       </c>
     </row>
@@ -5784,10 +5755,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5817,21 +5788,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5850,21 +5821,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5883,10 +5854,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -5916,21 +5887,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5949,21 +5920,21 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>1442</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>7/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5982,21 +5953,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -6015,10 +5986,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -6045,24 +6016,24 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>388</v>
+      </c>
+      <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="n">
-        <v>58</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -6081,21 +6052,21 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6114,10 +6085,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -6174,7 +6145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6234,7 +6205,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ATU On Campus</t>
+          <t>Korle Bu A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -6263,89 +6234,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Korle Bu A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Legon City</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6">
-        <f>SUM(C3:C5)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>SUM(D3:D5)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>SUM(E3:E5)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>SUM(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>F6&amp;"/"&amp;C6</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>SUM(H3:H5)</f>
+      <c r="C4">
+        <f>SUM(C3:C3)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>SUM(D3:D3)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUM(E3:E3)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>SUM(F3:F3)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>F4&amp;"/"&amp;C4</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>SUM(H3:H3)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -13,16 +13,15 @@
     <sheet name="Colossians 3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Colossians 4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Galatians 10" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 2 (Hold)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Galatians 3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 6 A" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,16 +481,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -506,13 +505,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
-        <v>1595</v>
+        <v>1871</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -530,16 +529,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>454</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -554,16 +553,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
-        <v>2688</v>
+        <v>644</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -581,37 +580,37 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" t="n">
-        <v>2352</v>
+        <v>618</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Isaac Agyeman</t>
+          <t>Nii Nkunim Armar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
+          <t>Galatians 10</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -629,205 +628,181 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="E9" t="n">
-        <v>3377</v>
+        <v>1663</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edwin Ogoe</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>656</v>
+        <v>634</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="E12" t="n">
-        <v>459</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="E13" t="n">
-        <v>2099</v>
+        <v>4119</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 7</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E14" t="n">
-        <v>2033</v>
+        <v>1158</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 8</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="E15" t="n">
-        <v>1334</v>
+        <v>2775</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Divine Olubakinde</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 9</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E16" t="n">
-        <v>3369</v>
+        <v>1945</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Galatians 9</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D17" t="n">
-        <v>124</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1294</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -841,13 +816,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 4</t>
         </is>
       </c>
     </row>
@@ -901,29 +876,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>440</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -934,229 +909,130 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Limann</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prince of Peace New</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revelations</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Edna Adorshie</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sarbah</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>219</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dennis Kpogli</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E9" t="n">
-        <v>125</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -1171,13 +1047,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 5</t>
         </is>
       </c>
     </row>
@@ -1231,95 +1107,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>115</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>75</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1330,64 +1206,295 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Galilea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lady Vanessa Osei</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>240</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GTUC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Richard Manu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>170</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GTUC Allos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>297</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kings/Regent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>210</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1545</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7">
-        <f>SUM(C3:C6)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>SUM(D3:D6)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>SUM(E3:E6)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>SUM(F3:F6)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>F7&amp;"/"&amp;C7</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>SUM(H3:H6)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -1402,13 +1509,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
     </row>
@@ -1462,121 +1569,121 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>175</v>
+        <v>306</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>135</v>
+        <v>1885</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1594,187 +1701,187 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>1125</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Diamond Jubilee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>15</v>
-      </c>
       <c r="E9" t="n">
-        <v>182</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kings/Regent</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1792,64 +1899,196 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stephanie Seglah</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>88</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C18">
+        <f>SUM(C3:C17)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>SUM(D3:D17)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>SUM(E3:E17)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>SUM(F3:F17)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>F18&amp;"/"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(H3:H17)</f>
         <v/>
       </c>
     </row>
@@ -1864,13 +2103,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 7</t>
         </is>
       </c>
     </row>
@@ -1924,29 +2163,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1957,29 +2196,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Akuafo Hall 1 New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Fredrick Anokye</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1990,62 +2229,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Akuafo Hall 2 New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Dacosta Amponsah</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Area 1  Logos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Erasmus Laryea</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2056,95 +2295,95 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Commonwealth 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Lois Osei</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2155,62 +2394,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2221,29 +2460,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2254,29 +2493,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>140</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2287,95 +2526,95 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elizabeth Obeng Adu</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2386,29 +2625,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2419,31 +2658,229 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E18" t="n">
+        <v>205</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>105</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>45</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18">
-        <f>SUM(C3:C17)</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>SUM(D3:D17)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>SUM(E3:E17)</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>SUM(F3:F17)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>F18&amp;"/"&amp;C18</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>SUM(H3:H17)</f>
+      <c r="C24">
+        <f>SUM(C3:C23)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>SUM(D3:D23)</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>SUM(E3:E23)</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>SUM(F3:F23)</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>F24&amp;"/"&amp;C24</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>SUM(H3:H23)</f>
         <v/>
       </c>
     </row>
@@ -2458,13 +2895,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 8</t>
         </is>
       </c>
     </row>
@@ -2518,62 +2955,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Charis</t>
+          <t>AKUAFO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stephen Asare Osei</t>
+          <t>Foanor Alloh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Hall 1 New</t>
+          <t>Akuafo Hall 6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fredrick Anokye</t>
+          <t>Ruby Nelson</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2584,121 +3021,121 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Akuafo Hall 2 New</t>
+          <t>Akuafo Zoe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dacosta Amponsah</t>
+          <t>Enoch Bentil</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>ELU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Tracy Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>625</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Legon hall</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Nana Ahema Forson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Legon Hall B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Yosi Forson</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -2716,85 +3153,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>695</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Volta Mega</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Doris Ainooh</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>425</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Volta Others</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Rachael Sekyiwaaa</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>20</v>
@@ -2815,427 +3252,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kwapong</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Eunice Owusu</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Legon Hall</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Edberg Ayensu</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="n">
-        <v>120</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4/3</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Main Campus Allos</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>38</v>
-      </c>
-      <c r="E14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Dunamis</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nana Kwame Barima</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>40</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main Campus Hagios</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Philmorra Laryea Okorley</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Main Campus Parakletos</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Melissa Meledi</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" t="n">
-        <v>75</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>24</v>
-      </c>
-      <c r="E18" t="n">
-        <v>150</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" t="n">
-        <v>95</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>80</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="n">
-        <v>95</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>12</v>
-      </c>
-      <c r="E22" t="n">
-        <v>90</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="n">
-        <v>40</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24">
-        <f>SUM(C3:C23)</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>SUM(D3:D23)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>SUM(E3:E23)</f>
-        <v/>
-      </c>
-      <c r="F24">
-        <f>SUM(F3:F23)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>F24&amp;"/"&amp;C24</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>SUM(H3:H23)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3250,426 +3291,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Galatians 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Governorship</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>No. Of Bacentas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Att</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Income(GHS)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No. Of Services</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Services/Bacentas</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Services Not Held</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AKUAFO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Foanor Alloh</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Akuafo Hall 6</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ruby Nelson</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Akuafo Zoe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Enoch Bentil</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E5" t="n">
-        <v>245</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ELU</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tracy Osei</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0/5</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Legon hall</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Nana Ahema Forson</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Legon Hall B</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Yosi Forson</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Caleb Osei-Kofi</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1642</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/9</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Volta Mega</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Doris Ainooh</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>36</v>
-      </c>
-      <c r="E10" t="n">
-        <v>447</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Volta Others</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rachael Sekyiwaaa</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>26</v>
-      </c>
-      <c r="E12" t="n">
-        <v>135</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3730,7 +3351,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Allos 1</t>
+          <t>UMC Allos 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3742,28 +3363,28 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Allos 2</t>
+          <t>UMC Allos 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3772,64 +3393,64 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Allos 3</t>
+          <t>UMC Allos 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marvellous Korsoku</t>
+          <t>Jessica Adonu</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>1101</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UPSA Allos 4</t>
+          <t>UMC Allos 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3841,28 +3462,28 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UPSA Allos 5</t>
+          <t>UMC Allos 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3874,10 +3495,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3895,7 +3516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UPSA Allos 6</t>
+          <t>UMC Allos 6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3907,28 +3528,28 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>228</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UPSA Allos 7</t>
+          <t>UMC Allos 7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3940,10 +3561,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -3961,7 +3582,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UPSA Allos 8</t>
+          <t>UMC Allos 8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3970,20 +3591,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
-        <v>374</v>
+        <v>174</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3994,7 +3615,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UPSA Allos 9</t>
+          <t>UMC Allos 9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4006,10 +3627,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -4131,28 +3752,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David Yalleh</t>
+          <t>Richard Anku</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4171,10 +3792,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4231,7 +3852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4306,7 +3927,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4333,20 +3954,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4369,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4402,21 +4023,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4435,21 +4056,21 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4468,21 +4089,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4501,10 +4122,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>295</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4534,10 +4155,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4564,20 +4185,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>693</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -4597,55 +4218,79 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1177</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -4660,7 +4305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4732,21 +4377,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4765,10 +4410,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4831,43 +4476,43 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Haatso Palace</t>
+          <t>Haatso West</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richard Anku</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4885,97 +4530,64 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Haatso West</t>
+          <t>THS Westland</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Sarpong</t>
+          <t>Joseph Halivor</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>THS Westland</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Joseph Halivor</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>73</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C9">
+        <f>SUM(C3:C8)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUM(D3:D8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E3:E8)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>F9&amp;"/"&amp;C9</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUM(H3:H8)</f>
         <v/>
       </c>
     </row>
@@ -5059,24 +4671,24 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
       <c r="E3" t="n">
-        <v>2498</v>
+        <v>250</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5092,20 +4704,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>271</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -5125,24 +4737,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5293,10 +4905,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>371</v>
+        <v>122</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5326,10 +4938,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -5362,18 +4974,18 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5392,10 +5004,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>1635</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -5425,10 +5037,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -5491,7 +5103,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
+          <t>Galatians 10</t>
         </is>
       </c>
     </row>
@@ -5590,10 +5202,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5623,21 +5235,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5755,10 +5367,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5788,10 +5400,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>416</v>
+        <v>250</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5821,10 +5433,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -5854,10 +5466,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -5887,10 +5499,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -5920,21 +5532,21 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>1442</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5953,21 +5565,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5986,10 +5598,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -6019,21 +5631,21 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>340</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -6052,21 +5664,21 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6085,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -6145,13 +5757,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 3</t>
         </is>
       </c>
     </row>
@@ -6205,25 +5817,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Korle Bu A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Campus Anagkazo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nayram Gblorkpor</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -6234,31 +5850,229 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Limann</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kwesi Boadu-Amoama</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mensah Sarbah Poimen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Prince Okai</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E5" t="n">
+        <v>112</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prince of Peace New</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Joseph Akyem</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Revelations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Edna Adorshie</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>228</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4">
-        <f>SUM(C3:C3)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>SUM(D3:D3)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>SUM(E3:E3)</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>SUM(F3:F3)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>F4&amp;"/"&amp;C4</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>SUM(H3:H3)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>259</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>1871</v>
+        <v>1431</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -532,10 +532,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>454</v>
+        <v>635</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>644</v>
+        <v>924</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>618</v>
+        <v>753</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -628,10 +628,10 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="E9" t="n">
-        <v>1663</v>
+        <v>1633</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="E10" t="n">
-        <v>755</v>
+        <v>901</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
-        <v>634</v>
+        <v>865</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>3449</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="E13" t="n">
-        <v>4119</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="E14" t="n">
-        <v>1158</v>
+        <v>1101</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="E15" t="n">
-        <v>2775</v>
+        <v>3946</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
-        <v>1945</v>
+        <v>4192</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,10 +954,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -990,7 +990,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>370</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1152,7 +1152,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>45</v>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>331</v>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4/7</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,10 +1218,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>2025</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1383,10 +1383,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1416,17 +1416,17 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>363</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>6/5</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1449,21 +1449,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>1545</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1581,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,10 +1647,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>1885</v>
+        <v>1790</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -1680,10 +1680,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1713,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1749,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1767,7 +1767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1779,10 +1779,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1812,10 +1812,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -1845,21 +1845,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1878,10 +1878,10 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1914,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1944,21 +1944,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>1007</v>
+        <v>990</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1977,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -2013,18 +2013,18 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2043,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2103,7 +2103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,21 +2208,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2241,21 +2241,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2274,21 +2274,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2307,40 +2307,40 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
@@ -2350,40 +2350,40 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2394,29 +2394,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2427,95 +2427,95 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2526,95 +2526,95 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Main Campus Dunamis</t>
+          <t>Main Campus Pistis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nana Kwame Barima</t>
+          <t>Richard Mawuli Sogbo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>6/5</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Main Campus Hagios</t>
+          <t>Main Campus Tsalach</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Philmorra Laryea Okorley</t>
+          <t>Jennifer Aidoo</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2625,29 +2625,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Main campus Zogreo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Elinam Fiagbe</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2658,29 +2658,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
+          <t>Volta Hall</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>Precious Antwi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2691,196 +2691,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>125</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>55</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>105</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>45</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24">
-        <f>SUM(C3:C23)</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>SUM(D3:D23)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>SUM(E3:E23)</f>
-        <v/>
-      </c>
-      <c r="F24">
-        <f>SUM(F3:F23)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>F24&amp;"/"&amp;C24</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>SUM(H3:H23)</f>
+      <c r="C19">
+        <f>SUM(C3:C18)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>SUM(D3:D18)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>SUM(E3:E18)</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>SUM(F3:F18)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>F19&amp;"/"&amp;C19</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H18)</f>
         <v/>
       </c>
     </row>
@@ -2895,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,24 +2799,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>285</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3000,21 +2835,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3033,10 +2868,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -3063,24 +2898,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>625</v>
+        <v>400</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3096,24 +2931,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3132,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -3162,24 +2997,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>695</v>
+        <v>390</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3198,21 +3033,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3234,7 +3069,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3252,31 +3087,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1565</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3363,10 +3222,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -3393,24 +3252,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3429,10 +3288,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>2973</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3462,10 +3321,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -3495,10 +3354,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3528,21 +3387,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>190</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3558,20 +3417,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -3594,10 +3453,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -3630,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -3687,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3752,28 +3611,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Richard Anku</t>
+          <t>David Yalleh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3792,52 +3651,85 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Spintex Palace</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Richard Anku</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C5">
-        <f>SUM(C3:C4)</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>SUM(D3:D4)</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>SUM(E3:E4)</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>SUM(F3:F4)</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>F5&amp;"/"&amp;C5</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>SUM(H3:H4)</f>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
         <v/>
       </c>
     </row>
@@ -3852,7 +3744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3924,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3957,10 +3849,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -3990,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -4023,21 +3915,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4056,21 +3948,21 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4122,10 +4014,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>1058</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4155,10 +4047,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4188,10 +4080,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -4221,7 +4113,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
@@ -4242,55 +4134,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>22</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1177</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -4377,10 +4245,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4509,10 +4377,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4545,7 +4413,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4674,21 +4542,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4707,10 +4575,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -4740,10 +4608,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -4905,10 +4773,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>122</v>
+        <v>401</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -4935,24 +4803,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4971,10 +4839,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -5001,20 +4869,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5037,21 +4905,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5202,21 +5070,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5367,10 +5235,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5400,10 +5268,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5433,10 +5301,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -5499,21 +5367,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5532,21 +5400,21 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5565,21 +5433,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5598,10 +5466,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -5631,10 +5499,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -5664,10 +5532,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -5697,10 +5565,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -5757,7 +5625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5829,10 +5697,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -5850,29 +5718,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Limann</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -5883,29 +5751,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5916,29 +5784,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prince of Peace New</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5949,29 +5817,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revelations</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edna Adorshie</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5982,29 +5850,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sarbah</t>
+          <t>Main Campus Proskuneo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Isaac Baidoo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -6015,29 +5883,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sey</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -6048,31 +5916,196 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Prince of Peace New</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Joseph Akyem</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Revelations</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Edna Adorshie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>176</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C15">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>F15&amp;"/"&amp;C15</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUM(H3:H14)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>1938</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>1431</v>
+        <v>5184</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>635</v>
+        <v>3187</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>924</v>
+        <v>3524</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
-        <v>753</v>
+        <v>1644</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E9" t="n">
-        <v>1633</v>
+        <v>2604</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>901</v>
+        <v>1336</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>865</v>
+        <v>681</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>3449</v>
+        <v>4816</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>1348</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E14" t="n">
-        <v>1101</v>
+        <v>1357</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -772,10 +772,10 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E15" t="n">
-        <v>3946</v>
+        <v>2680</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="E16" t="n">
-        <v>4192</v>
+        <v>2697</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -891,18 +891,18 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1152,21 +1152,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>331</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1221,7 +1221,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1251,21 +1251,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>2025</v>
+        <v>1230</v>
       </c>
       <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>365</v>
+        <v>1890</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1383,21 +1383,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,17 +1416,17 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>363</v>
+        <v>615</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1449,21 +1449,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1581,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,10 +1647,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>1790</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -1680,10 +1680,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1713,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1746,10 +1746,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1779,10 +1779,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1812,10 +1812,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -1845,21 +1845,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1878,10 +1878,10 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1977,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -2010,21 +2010,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2043,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2208,21 +2208,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2241,21 +2241,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2274,21 +2274,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2307,17 +2307,17 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -2406,10 +2406,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -2439,10 +2439,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -2472,21 +2472,21 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -2505,21 +2505,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2571,17 +2571,17 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2604,21 +2604,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2637,17 +2637,17 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2670,10 +2670,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -2802,10 +2802,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>285</v>
+        <v>415</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2835,21 +2835,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2868,10 +2868,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2904,7 +2904,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2970,7 +2970,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -3000,10 +3000,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>390</v>
+        <v>215</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -3033,21 +3033,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>471</v>
+        <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3092,10 +3092,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
-        <v>1565</v>
+        <v>1180</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3150,7 +3150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,21 +3222,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3255,10 +3255,10 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -3288,10 +3288,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>2973</v>
+        <v>376</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3321,21 +3321,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3354,10 +3354,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3387,10 +3387,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -3420,10 +3420,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -3453,10 +3453,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -3486,52 +3486,76 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1256</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3618,21 +3642,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1779</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3651,21 +3675,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3684,21 +3708,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3816,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -3849,10 +3873,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -3882,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -3915,21 +3939,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3948,10 +3972,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4014,10 +4038,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>1058</v>
+        <v>4546</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4047,10 +4071,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>310</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4080,10 +4104,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -4113,10 +4137,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -4245,10 +4269,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4281,7 +4305,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>2078</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4311,21 +4335,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4344,21 +4368,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4377,10 +4401,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>302</v>
+        <v>762</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4410,10 +4434,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4542,21 +4566,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>450</v>
+        <v>3249</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4575,21 +4599,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>324</v>
+        <v>145</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4608,10 +4632,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -4773,21 +4797,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>401</v>
+        <v>473</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4809,7 +4833,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>495</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -4839,21 +4863,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4872,21 +4896,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4905,21 +4929,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5163,7 +5187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5235,10 +5259,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5261,24 +5285,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Agbesi</t>
+          <t>Emmanuel Otiboe</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
-        <v>340</v>
+        <v>1020</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -5298,20 +5322,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5322,29 +5346,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arena Allos</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eric Akoto</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5355,29 +5379,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5388,62 +5412,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5454,29 +5478,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>545</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -5487,29 +5511,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>UssherFort</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Seth Kpelebe</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -5520,29 +5544,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Yours and Ours</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Prince Odum</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -5553,64 +5577,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Emmanuel Otiboe</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="n">
-        <v>201</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -5733,7 +5724,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5763,7 +5754,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>60</v>
@@ -5796,10 +5787,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5829,17 +5820,17 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5862,7 +5853,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>85</v>
@@ -5895,10 +5886,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5928,10 +5919,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -5961,10 +5952,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -5994,21 +5985,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6030,7 +6021,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>556</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -6060,21 +6051,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,10 +484,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>1938</v>
+        <v>190</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -508,10 +508,10 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>5184</v>
+        <v>1167</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>3187</v>
+        <v>1409</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>3524</v>
+        <v>2655</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>1644</v>
+        <v>2463</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="E9" t="n">
-        <v>2604</v>
+        <v>1466</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E10" t="n">
-        <v>1336</v>
+        <v>767</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -676,10 +676,10 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>681</v>
+        <v>568</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E12" t="n">
-        <v>4816</v>
+        <v>1675</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="E13" t="n">
-        <v>1348</v>
+        <v>2105</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="E14" t="n">
-        <v>1357</v>
+        <v>991</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="E15" t="n">
-        <v>2680</v>
+        <v>3172</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="E16" t="n">
-        <v>2697</v>
+        <v>5284</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -888,10 +888,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1149,24 +1149,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1185,76 +1185,76 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>GCTU Koinonia Governorship</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Christabel Tukpeyi</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1230</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1314,24 +1314,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>1890</v>
+        <v>655</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1347,20 +1347,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1383,50 +1383,50 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kings/Regent</t>
+          <t>Kings University</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>615</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1449,52 +1449,85 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>5</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5/9</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Regent University</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>513</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C15">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>F15&amp;"/"&amp;C15</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUM(H3:H14)</f>
         <v/>
       </c>
     </row>
@@ -1581,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,10 +1647,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1647,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -1680,10 +1713,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1713,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>105</v>
@@ -1746,10 +1779,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1779,10 +1812,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1809,20 +1842,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1845,21 +1878,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1881,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1914,7 +1947,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1944,10 +1977,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>819</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -1980,7 +2013,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -2010,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -2046,7 +2079,7 @@
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2172,20 +2205,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2208,21 +2241,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2241,21 +2274,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2274,10 +2307,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -2307,17 +2340,17 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2340,10 +2373,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -2373,10 +2406,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -2406,10 +2439,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -2439,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2469,24 +2502,24 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -2505,7 +2538,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
@@ -2538,10 +2571,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2568,20 +2601,20 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2604,10 +2637,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>365</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -2637,10 +2670,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2670,21 +2703,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2802,21 +2835,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>415</v>
+        <v>540</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2835,10 +2868,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2868,10 +2901,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2901,21 +2934,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2937,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2967,21 +3000,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3000,21 +3033,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3033,21 +3066,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3066,10 +3099,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3092,10 +3125,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
-        <v>1180</v>
+        <v>797</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3150,7 +3183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,10 +3255,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -3255,21 +3288,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3288,10 +3321,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>376</v>
+        <v>4432</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3321,10 +3354,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -3357,7 +3390,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3387,21 +3420,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3420,10 +3453,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -3456,7 +3489,7 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -3486,76 +3519,52 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>58</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1256</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3642,10 +3651,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1779</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3678,7 +3687,7 @@
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3840,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3873,10 +3882,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -3906,10 +3915,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3939,21 +3948,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3972,10 +3981,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4038,10 +4047,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>4546</v>
+        <v>650</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4071,21 +4080,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>310</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4104,10 +4113,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -4140,7 +4149,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -4269,10 +4278,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4305,7 +4314,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2078</v>
+        <v>1253</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4335,21 +4344,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4368,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
@@ -4401,10 +4410,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>762</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4434,10 +4443,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4566,10 +4575,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>3249</v>
+        <v>2420</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -4599,21 +4608,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4632,21 +4641,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4797,10 +4806,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>473</v>
+        <v>551</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -4830,21 +4839,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>495</v>
+        <v>676</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4863,10 +4872,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4896,10 +4905,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>195</v>
+        <v>1053</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -4929,17 +4938,17 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -5262,7 +5271,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5289,24 +5298,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>1020</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5325,10 +5334,10 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -5355,20 +5364,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5391,21 +5400,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5424,21 +5433,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5457,17 +5466,17 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5490,10 +5499,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>545</v>
+        <v>320</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -5559,7 +5568,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -5616,7 +5625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5691,7 +5700,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -5721,10 +5730,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5754,10 +5763,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -5787,10 +5796,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5820,21 +5829,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5853,10 +5862,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -5886,10 +5895,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5922,7 +5931,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -5985,21 +5994,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>4</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4/7</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6015,24 +6024,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>556</v>
+        <v>121</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6051,10 +6060,10 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -6072,31 +6081,64 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Shemen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samuel Agyei</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>SUM(E3:E14)</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>SUM(F3:F14)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>F15&amp;"/"&amp;C15</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>SUM(H3:H14)</f>
+      <c r="C16">
+        <f>SUM(C3:C15)</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>SUM(D3:D15)</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>SUM(E3:E15)</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>SUM(F3:F15)</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>F16&amp;"/"&amp;C16</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>SUM(H3:H15)</f>
         <v/>
       </c>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
-        <v>1167</v>
+        <v>1003</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1409</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>2655</v>
+        <v>2434</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>2463</v>
+        <v>540</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>1466</v>
+        <v>2708</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>1675</v>
+        <v>1456</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2105</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E14" t="n">
-        <v>991</v>
+        <v>921</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
-        <v>3172</v>
+        <v>3295</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>5284</v>
+        <v>3197</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,21 +1218,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1251,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>655</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1350,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1383,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,21 +1416,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>0/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1482,21 +1482,21 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
-        <v>513</v>
+        <v>1446</v>
       </c>
       <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>4</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1647,21 +1647,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1680,21 +1680,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1710,418 +1710,451 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Block A Beta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Gracy Wellington</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>25</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>819</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Stephanie Seglah</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18">
-        <f>SUM(C3:C17)</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>SUM(D3:D17)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>SUM(E3:E17)</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>SUM(F3:F17)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>F18&amp;"/"&amp;C18</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>SUM(H3:H17)</f>
+      <c r="C19">
+        <f>SUM(C3:C18)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>SUM(D3:D18)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>SUM(E3:E18)</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>SUM(F3:F18)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>F19&amp;"/"&amp;C19</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H18)</f>
         <v/>
       </c>
     </row>
@@ -2136,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,21 +2241,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2241,21 +2274,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2274,21 +2307,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2307,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2340,21 +2373,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2373,21 +2406,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2406,21 +2439,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2439,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2472,21 +2505,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2538,21 +2571,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2571,21 +2604,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2604,21 +2637,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>7</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2637,21 +2670,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2670,21 +2703,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2703,52 +2736,76 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>141</v>
+      </c>
+      <c r="E19" t="n">
+        <v>921</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19">
-        <f>SUM(C3:C18)</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>SUM(D3:D18)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>SUM(E3:E18)</f>
-        <v/>
-      </c>
-      <c r="F19">
-        <f>SUM(F3:F18)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>F19&amp;"/"&amp;C19</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>SUM(H3:H18)</f>
+      <c r="C20">
+        <f>SUM(C3:C19)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>SUM(D3:D19)</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>SUM(E3:E19)</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>SUM(F3:F19)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>F20&amp;"/"&amp;C20</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>SUM(H3:H19)</f>
         <v/>
       </c>
     </row>
@@ -2835,21 +2892,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2868,21 +2925,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2901,21 +2958,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2934,21 +2991,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2967,21 +3024,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3000,21 +3057,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3033,21 +3090,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3066,21 +3123,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3099,21 +3156,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3125,10 +3182,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>797</v>
+        <v>3295</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3183,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3255,21 +3312,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3288,21 +3345,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3321,21 +3378,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4432</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3354,21 +3411,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3387,21 +3444,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3420,21 +3477,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3453,21 +3510,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>4</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3486,21 +3543,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3519,52 +3576,76 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>117</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3651,21 +3732,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3684,21 +3765,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3777,7 +3858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3849,21 +3930,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3882,21 +3963,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3915,21 +3996,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3948,21 +4029,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3981,21 +4062,21 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4047,21 +4128,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4080,21 +4161,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4113,21 +4194,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -4146,52 +4227,76 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="n">
+        <v>968</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -4278,21 +4383,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4311,21 +4416,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1253</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4377,21 +4482,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4410,21 +4515,21 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4443,21 +4548,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4503,7 +4608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4575,21 +4680,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2420</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4608,21 +4713,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4641,52 +4746,76 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2434</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6">
-        <f>SUM(C3:C5)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>SUM(D3:D5)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>SUM(E3:E5)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>SUM(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>F6&amp;"/"&amp;C6</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>SUM(H3:H5)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -4701,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4806,21 +4935,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4839,21 +4968,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4872,21 +5001,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4905,21 +5034,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1053</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4938,52 +5067,76 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>540</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9">
-        <f>SUM(C3:C8)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>SUM(D3:D8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E3:E8)</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>SUM(F3:F8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>F9&amp;"/"&amp;C9</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>SUM(H3:H8)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -5196,7 +5349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5268,21 +5421,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5301,21 +5454,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5334,21 +5487,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5367,21 +5520,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5400,21 +5553,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5433,21 +5586,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5466,21 +5619,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5499,21 +5652,21 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5532,21 +5685,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -5565,52 +5718,76 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2708</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -5697,21 +5874,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5730,21 +5907,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5763,21 +5940,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5796,21 +5973,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5829,21 +6006,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5862,21 +6039,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5895,21 +6072,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5928,21 +6105,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5961,21 +6138,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -5994,21 +6171,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6027,21 +6204,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6060,21 +6237,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -6093,21 +6270,21 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>1003</v>
+        <v>769</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>2434</v>
+        <v>242</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="E9" t="n">
-        <v>2708</v>
+        <v>1305</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>1456</v>
+        <v>2842</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2803</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E14" t="n">
-        <v>921</v>
+        <v>968</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>172</v>
       </c>
       <c r="E15" t="n">
-        <v>3295</v>
+        <v>6102</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E16" t="n">
-        <v>3197</v>
+        <v>4250</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1152,21 +1152,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1218,21 +1218,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1350,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1383,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,21 +1416,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1482,21 +1482,21 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>1446</v>
+        <v>389</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1647,21 +1647,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1680,21 +1680,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1713,21 +1713,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1746,21 +1746,21 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1779,21 +1779,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1812,21 +1812,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1845,21 +1845,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1878,21 +1878,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1977,21 +1977,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2010,21 +2010,21 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1505</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,21 +2043,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2076,21 +2076,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2109,21 +2109,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2169,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,21 +2241,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2274,21 +2274,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2307,21 +2307,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2373,21 +2373,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2406,21 +2406,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2439,21 +2439,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2472,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2505,21 +2505,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2604,21 +2604,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2637,21 +2637,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2670,21 +2670,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2703,21 +2703,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2736,76 +2736,52 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>141</v>
-      </c>
-      <c r="E19" t="n">
-        <v>921</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C20">
-        <f>SUM(C3:C19)</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>SUM(D3:D19)</f>
-        <v/>
-      </c>
-      <c r="E20">
-        <f>SUM(E3:E19)</f>
-        <v/>
-      </c>
-      <c r="F20">
-        <f>SUM(F3:F19)</f>
-        <v/>
-      </c>
-      <c r="G20">
-        <f>F20&amp;"/"&amp;C20</f>
-        <v/>
-      </c>
-      <c r="H20">
-        <f>SUM(H3:H19)</f>
+      <c r="C19">
+        <f>SUM(C3:C18)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>SUM(D3:D18)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>SUM(E3:E18)</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>SUM(F3:F18)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>F19&amp;"/"&amp;C19</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H18)</f>
         <v/>
       </c>
     </row>
@@ -2892,21 +2868,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2925,21 +2901,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2958,21 +2934,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2991,21 +2967,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3024,21 +3000,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3057,21 +3033,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3090,21 +3066,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1563</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3123,21 +3099,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3156,21 +3132,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3182,10 +3158,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>3295</v>
+        <v>2711</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3240,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3312,21 +3288,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3345,21 +3321,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>6/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3378,21 +3354,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3283</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3411,21 +3387,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3444,21 +3420,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3477,21 +3453,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3510,21 +3486,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3543,21 +3519,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3576,76 +3552,52 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>117</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3729,24 +3681,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3765,21 +3717,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3798,21 +3750,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3858,7 +3810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3930,21 +3882,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3963,21 +3915,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3996,21 +3948,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4029,21 +3981,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4062,10 +4014,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -4128,21 +4080,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4161,21 +4113,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4194,21 +4146,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -4248,55 +4200,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" t="n">
-        <v>968</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -4383,21 +4311,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4416,21 +4344,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4482,21 +4410,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4515,21 +4443,21 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4548,21 +4476,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4608,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4713,21 +4641,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4746,76 +4674,52 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>37</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2434</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7">
-        <f>SUM(C3:C6)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>SUM(D3:D6)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>SUM(E3:E6)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>SUM(F3:F6)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>F7&amp;"/"&amp;C7</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>SUM(H3:H6)</f>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUM(E3:E5)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUM(F3:F5)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6&amp;"/"&amp;C6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(H3:H5)</f>
         <v/>
       </c>
     </row>
@@ -4830,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4935,21 +4839,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4968,21 +4872,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5001,21 +4905,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5034,21 +4938,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5067,76 +4971,52 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="D9" t="n">
-        <v>22</v>
-      </c>
-      <c r="E9" t="n">
-        <v>540</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C9">
+        <f>SUM(C3:C8)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUM(D3:D8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E3:E8)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>F9&amp;"/"&amp;C9</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUM(H3:H8)</f>
         <v/>
       </c>
     </row>
@@ -5349,7 +5229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5421,21 +5301,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5454,21 +5334,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5487,21 +5367,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5520,21 +5400,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5553,21 +5433,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5586,21 +5466,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5619,21 +5499,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5652,21 +5532,21 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5685,21 +5565,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -5718,76 +5598,52 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2708</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -5874,21 +5730,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5907,21 +5763,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5940,21 +5796,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5973,21 +5829,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -6039,21 +5895,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -6072,21 +5928,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -6105,21 +5961,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -6138,21 +5994,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -6171,21 +6027,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6204,21 +6060,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6237,21 +6093,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -6270,21 +6126,21 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>1035</v>
+        <v>1289</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
-        <v>769</v>
+        <v>5241</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>1351</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>242</v>
+        <v>3478</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="E7" t="n">
-        <v>558</v>
+        <v>1761</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="E9" t="n">
-        <v>1305</v>
+        <v>2562</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E10" t="n">
-        <v>853</v>
+        <v>1314</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>625</v>
+        <v>1062</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E12" t="n">
-        <v>2842</v>
+        <v>3081</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="E13" t="n">
-        <v>2803</v>
+        <v>2974</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="E14" t="n">
-        <v>968</v>
+        <v>913</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="E15" t="n">
-        <v>6102</v>
+        <v>1731</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>4250</v>
+        <v>2277</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>315</v>
+        <v>393</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>310</v>
+        <v>504</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1152,10 +1152,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1218,21 +1218,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1251,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1284,10 +1284,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>2050</v>
+        <v>1050</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -1317,10 +1317,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1350,10 +1350,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1383,10 +1383,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1449,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1485,18 +1485,18 @@
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>389</v>
+        <v>706</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1614,10 +1614,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -1647,10 +1647,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1680,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>147</v>
+        <v>1940</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -1746,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1782,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1812,10 +1812,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1848,7 +1848,7 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1944,7 +1944,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
         <v>210</v>
@@ -1977,21 +1977,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2010,21 +2010,21 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>1505</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,21 +2043,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2073,20 +2073,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2106,20 +2106,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2241,21 +2241,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2274,21 +2274,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2307,17 +2307,17 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2376,7 +2376,7 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -2409,7 +2409,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -2442,7 +2442,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -2472,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2604,10 +2604,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2637,10 +2637,10 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -2670,10 +2670,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -2703,10 +2703,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2736,21 +2736,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2871,18 +2871,18 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>259</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2901,10 +2901,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2934,10 +2934,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2967,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>420</v>
+        <v>342</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -3000,10 +3000,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -3033,21 +3033,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3069,7 +3069,7 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>1563</v>
+        <v>435</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -3099,21 +3099,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>363</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3132,10 +3132,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3153,55 +3153,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>69</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2711</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3216,7 +3192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3281,57 +3257,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Papa Kojo Amoakwa</t>
+          <t>Herbert Aidoo</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>117</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UMC Allos 2</t>
+          <t>UMC Allos 10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Herbert Aidoo</t>
+          <t>Doreen Nartey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3342,128 +3318,128 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UMC Allos 3</t>
+          <t>UMC Allos 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jessica Adonu</t>
+          <t>Papa Kojo Amoakwa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>3283</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UMC Allos 4</t>
+          <t>UMC Allos 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Linda Tunkum</t>
+          <t>Jessica Adonu</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>1717</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UMC Allos 5</t>
+          <t>UMC Allos 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joshua Agymang</t>
+          <t>Linda Tunkum</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UMC Allos 6</t>
+          <t>UMC Allos 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David Abuaku</t>
+          <t>Joshua Agymang</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3474,73 +3450,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UMC Allos 7</t>
+          <t>UMC Allos 6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blessing Umukoro</t>
+          <t>David Abuaku</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UMC Allos 8</t>
+          <t>UMC Allos 7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Divine Olubakinde</t>
+          <t>Blessing Umukoro</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UMC Allos 9</t>
+          <t>UMC Allos 8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3573,31 +3549,97 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>UMC Allos 9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nancy Kubi</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UMC E-Church</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -3684,21 +3726,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>855</v>
+        <v>1127</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3717,10 +3759,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3753,7 +3795,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3882,10 +3924,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3915,10 +3957,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -3951,7 +3993,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3981,21 +4023,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4014,21 +4056,21 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4080,10 +4122,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>440</v>
+        <v>4903</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4113,21 +4155,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4149,7 +4191,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4311,21 +4353,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4344,21 +4386,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4410,10 +4452,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -4443,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>810</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4479,7 +4521,7 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4608,21 +4650,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3204</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4641,10 +4683,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -4674,21 +4716,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4734,7 +4776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4799,28 +4841,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Princess Gueyennevievarl Wilson-Anderson</t>
+          <t>Sheryl Azu</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4839,21 +4881,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4872,21 +4914,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4905,10 +4947,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4938,21 +4980,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4968,55 +5010,112 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Wisconsin Haatso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Amanda Tenu</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>160</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>634</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9">
-        <f>SUM(C3:C8)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>SUM(D3:D8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E3:E8)</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>SUM(F3:F8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>F9&amp;"/"&amp;C9</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>SUM(H3:H8)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -5301,10 +5400,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5334,21 +5433,21 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5367,10 +5466,10 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -5400,21 +5499,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5433,21 +5532,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>970</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5466,10 +5565,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -5502,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5532,10 +5631,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>170</v>
+        <v>465</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -5565,10 +5664,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -5598,7 +5697,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>60</v>
@@ -5763,10 +5862,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5796,10 +5895,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -5829,10 +5928,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5895,21 +5994,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5928,10 +6027,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5961,10 +6060,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -5997,7 +6096,7 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -6027,21 +6126,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>4</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4/7</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6060,21 +6159,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>144</v>
+        <v>611</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6093,21 +6192,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
